--- a/data/raw/김포 25년/항공통계상세조회(노선) (7).xlsx
+++ b/data/raw/김포 25년/항공통계상세조회(노선) (7).xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="69">
   <si>
     <t>SEQ</t>
   </si>
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>10810</t>
-  </si>
-  <si>
-    <t>1901735</t>
-  </si>
-  <si>
-    <t>14658</t>
+    <t>5417</t>
+  </si>
+  <si>
+    <t>973716</t>
+  </si>
+  <si>
+    <t>7716</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,175 +53,172 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
-    <t>67423</t>
-  </si>
-  <si>
-    <t>725</t>
+    <t>217</t>
+  </si>
+  <si>
+    <t>33860</t>
+  </si>
+  <si>
+    <t>395</t>
   </si>
   <si>
     <t>광주(KWJ)</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>12125</t>
-  </si>
-  <si>
-    <t>34</t>
+    <t>57</t>
+  </si>
+  <si>
+    <t>5898</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>김해(PUS)</t>
   </si>
   <si>
-    <t>1389</t>
-  </si>
-  <si>
-    <t>205106</t>
-  </si>
-  <si>
-    <t>777</t>
+    <t>698</t>
+  </si>
+  <si>
+    <t>103468</t>
+  </si>
+  <si>
+    <t>379</t>
   </si>
   <si>
     <t>나고야(NGO)</t>
   </si>
   <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>4426</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>5391</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>77589</t>
+  </si>
+  <si>
+    <t>1442</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>13418</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>7162</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
+  </si>
+  <si>
     <t>62</t>
   </si>
   <si>
-    <t>9191</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>10923</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>743</t>
-  </si>
-  <si>
-    <t>151519</t>
-  </si>
-  <si>
-    <t>2220</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>26503</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>14189</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>20316</t>
-  </si>
-  <si>
-    <t>237</t>
+    <t>10569</t>
+  </si>
+  <si>
+    <t>139</t>
   </si>
   <si>
     <t>여수(RSU)</t>
   </si>
   <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>19234</t>
+    <t>87</t>
+  </si>
+  <si>
+    <t>9588</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
   <si>
     <t>울산(USN)</t>
   </si>
   <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>20813</t>
-  </si>
-  <si>
-    <t>69</t>
+    <t>89</t>
+  </si>
+  <si>
+    <t>10201</t>
+  </si>
+  <si>
+    <t>35</t>
   </si>
   <si>
     <t>제주(CJU)</t>
   </si>
   <si>
-    <t>6852</t>
-  </si>
-  <si>
-    <t>1271382</t>
-  </si>
-  <si>
-    <t>8841</t>
+    <t>3431</t>
+  </si>
+  <si>
+    <t>654960</t>
+  </si>
+  <si>
+    <t>4546</t>
   </si>
   <si>
     <t>카오슝(KHH)</t>
   </si>
   <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>12243</t>
-  </si>
-  <si>
-    <t>129</t>
+    <t>37</t>
+  </si>
+  <si>
+    <t>6215</t>
   </si>
   <si>
     <t>포항 경주(KPO)</t>
   </si>
   <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>3692</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>1982</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>홍차오(SHA)</t>
   </si>
   <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>57076</t>
-  </si>
-  <si>
-    <t>1015</t>
+    <t>123</t>
+  </si>
+  <si>
+    <t>28989</t>
+  </si>
+  <si>
+    <t>352</t>
   </si>
 </sst>
 </file>
@@ -472,7 +469,7 @@
         <v>41</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -483,16 +480,16 @@
         <v>11</v>
       </c>
       <c r="C11" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="D11" t="s" s="0">
+      <c r="E11" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="E11" t="s" s="0">
+      <c r="F11" t="s" s="0">
         <v>45</v>
-      </c>
-      <c r="F11" t="s" s="0">
-        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -503,16 +500,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="D12" t="s" s="0">
+      <c r="E12" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="E12" t="s" s="0">
+      <c r="F12" t="s" s="0">
         <v>49</v>
-      </c>
-      <c r="F12" t="s" s="0">
-        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -572,7 +569,7 @@
         <v>60</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>61</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -583,16 +580,16 @@
         <v>11</v>
       </c>
       <c r="C16" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="D16" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="D16" t="s" s="0">
+      <c r="E16" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="E16" t="s" s="0">
+      <c r="F16" t="s" s="0">
         <v>64</v>
-      </c>
-      <c r="F16" t="s" s="0">
-        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -603,16 +600,16 @@
         <v>11</v>
       </c>
       <c r="C17" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="D17" t="s" s="0">
+      <c r="E17" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="E17" t="s" s="0">
+      <c r="F17" t="s" s="0">
         <v>68</v>
-      </c>
-      <c r="F17" t="s" s="0">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
